--- a/data/lossofsale_sg_edappal.xlsx
+++ b/data/lossofsale_sg_edappal.xlsx
@@ -3926,6 +3926,377 @@
         </is>
       </c>
     </row>
+    <row r="72">
+      <c r="A72" s="65">
+        <v>70</v>
+      </c>
+      <c t="inlineStr" r="B72">
+        <is>
+          <t xml:space="preserve">26-12-2025</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C72">
+        <is>
+          <t xml:space="preserve">Akshay</t>
+        </is>
+      </c>
+      <c r="D72" s="65">
+        <v>9048952588</v>
+      </c>
+      <c t="inlineStr" r="E72">
+        <is>
+          <t xml:space="preserve">29-12-2025</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="F72">
+        <is>
+          <t xml:space="preserve">AKSHAY. V</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="G72">
+        <is>
+          <t xml:space="preserve">Loss</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="H72">
+        <is>
+          <t xml:space="preserve">PRODUCT</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="I72">
+        <is>
+          <t xml:space="preserve">PRODUCT NOT AVAILABLE</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="J72">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="K72">
+        <is>
+          <t xml:space="preserve">lite pink kurutha embroidery wrok one side not available</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="65">
+        <v>71</v>
+      </c>
+      <c t="inlineStr" r="B73">
+        <is>
+          <t xml:space="preserve">27-12-2025</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C73">
+        <is>
+          <t xml:space="preserve">Hamsath</t>
+        </is>
+      </c>
+      <c r="D73" s="65">
+        <v>9946995432</v>
+      </c>
+      <c t="inlineStr" r="E73">
+        <is>
+          <t xml:space="preserve">07-01-2026</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="F73">
+        <is>
+          <t xml:space="preserve">AKSHAY. V</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="G73">
+        <is>
+          <t xml:space="preserve">Loss</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="H73">
+        <is>
+          <t xml:space="preserve">CUSTOMER INTERNAL ISSUES</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="I73">
+        <is>
+          <t xml:space="preserve">FAMILY DISAPPROVEL</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="J73">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="K73">
+        <is>
+          <t xml:space="preserve">they will decide after confirming with their family in two days</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="65">
+        <v>72</v>
+      </c>
+      <c t="inlineStr" r="B74">
+        <is>
+          <t xml:space="preserve">27-12-2025</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C74">
+        <is>
+          <t xml:space="preserve">jasir</t>
+        </is>
+      </c>
+      <c r="D74" s="65">
+        <v>9946780363</v>
+      </c>
+      <c t="inlineStr" r="E74">
+        <is>
+          <t xml:space="preserve">08-01-2026</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="F74">
+        <is>
+          <t xml:space="preserve">MUHAMMED RAFI P V</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="G74">
+        <is>
+          <t xml:space="preserve">Loss</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="H74">
+        <is>
+          <t xml:space="preserve">PRODUCT</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="I74">
+        <is>
+          <t xml:space="preserve">Product Already Booked</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="J74">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="K74">
+        <is>
+          <t xml:space="preserve">The customer wanted a coffee brown suit, but the suit rentout. So 30th came and said they could try it out and then book it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="65">
+        <v>73</v>
+      </c>
+      <c t="inlineStr" r="B75">
+        <is>
+          <t xml:space="preserve">28-12-2025</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C75">
+        <is>
+          <t xml:space="preserve">AJMAL</t>
+        </is>
+      </c>
+      <c r="D75" s="65">
+        <v>7558806829</v>
+      </c>
+      <c t="inlineStr" r="E75">
+        <is>
+          <t xml:space="preserve">31-12-2025</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="F75">
+        <is>
+          <t xml:space="preserve">SHAHEEN</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="G75">
+        <is>
+          <t xml:space="preserve">Loss</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="H75">
+        <is>
+          <t xml:space="preserve">CUSTOMER INTERNAL ISSUES</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="I75">
+        <is>
+          <t xml:space="preserve">FAMILY DISAPPROVEL</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="J75">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="K75">
+        <is>
+          <t xml:space="preserve">CUSTOMER NEED TO DISCUSS WITH THEIR FAMILY</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="65">
+        <v>74</v>
+      </c>
+      <c t="inlineStr" r="B76">
+        <is>
+          <t xml:space="preserve">28-12-2025</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C76">
+        <is>
+          <t xml:space="preserve">prabeesh</t>
+        </is>
+      </c>
+      <c r="D76" s="65">
+        <v>9169161990</v>
+      </c>
+      <c t="inlineStr" r="E76">
+        <is>
+          <t xml:space="preserve">09-01-2026</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="F76">
+        <is>
+          <t xml:space="preserve">MUHAMMED RAFI P V</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="G76">
+        <is>
+          <t xml:space="preserve">Loss</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="H76">
+        <is>
+          <t xml:space="preserve">CUSTOMER INTERNAL ISSUES</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="I76">
+        <is>
+          <t xml:space="preserve">FAMILY DISAPPROVEL</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="J76">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="K76">
+        <is>
+          <t xml:space="preserve">need time to confirm with family</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="65">
+        <v>75</v>
+      </c>
+      <c t="inlineStr" r="B77">
+        <is>
+          <t xml:space="preserve">29-12-2025</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C77">
+        <is>
+          <t xml:space="preserve">Ajshan</t>
+        </is>
+      </c>
+      <c r="D77" s="65">
+        <v>8714147374</v>
+      </c>
+      <c t="inlineStr" r="E77">
+        <is>
+          <t xml:space="preserve">10-01-2026</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="F77">
+        <is>
+          <t xml:space="preserve">AKSHAY. V</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="G77">
+        <is>
+          <t xml:space="preserve">Loss</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="H77">
+        <is>
+          <t xml:space="preserve">CUSTOMER INTERNAL ISSUES</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="I77">
+        <is>
+          <t xml:space="preserve">FAMILY DISAPPROVEL</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="J77">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="K77">
+        <is>
+          <t xml:space="preserve">they will decide after confirming with their family in two days</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="65">
+        <v>76</v>
+      </c>
+      <c t="inlineStr" r="B78">
+        <is>
+          <t xml:space="preserve">29-12-2025</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C78">
+        <is>
+          <t xml:space="preserve">Rashi</t>
+        </is>
+      </c>
+      <c r="D78" s="65">
+        <v>7736769551</v>
+      </c>
+      <c t="inlineStr" r="E78">
+        <is>
+          <t xml:space="preserve">03-01-2026</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="F78">
+        <is>
+          <t xml:space="preserve">AKSHAY. V</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="G78">
+        <is>
+          <t xml:space="preserve">Loss</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="H78">
+        <is>
+          <t xml:space="preserve">PRODUCT</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="I78">
+        <is>
+          <t xml:space="preserve">PRODUCT NOT AVAILABLE</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="J78">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="K78">
+        <is>
+          <t xml:space="preserve">The customer wanted bootcut pants, but we didn't have them in stock, so the customer said no for that reason.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:K1"/>
